--- a/XlsxSharp.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
+++ b/XlsxSharp.Tests/Resource/Examples/Misc/FormulasWithEvaluation.xlsx
@@ -1,74 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Formulas" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames>
-    <x:definedName name="A10_R1C1_A10_R1C1">Formulas!$A$10:$A$10</x:definedName>
-  </x:definedNames>
-  <x:calcPr calcId="125725" calcMode="auto" refMode="R1C1"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Formulas" sheetId="1"/>
+  </sheets>
+  <definedNames>
+    <definedName name="A10_R1C1_A10_R1C1">Formulas!$A$10:$A$10</definedName>
+  </definedNames>
+  <calcPr calcId="125725" calcMode="auto" refMode="R1C1"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Num1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Num2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cell.FormulaA1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cell.FormulaR1C1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cell.Value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Are Equal?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A2+$B$2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RC[-2]+R2C2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A3+$B$3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RC[-2]+R3C2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"Test" &amp; A4 &amp; "R3C2"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"Test" &amp; RC[-2] &amp; "R3C2"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TestAR3C2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Array Formula: </x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Num1</t>
+  </si>
+  <si>
+    <t>Num2</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>cell.FormulaA1</t>
+  </si>
+  <si>
+    <t>cell.FormulaR1C1</t>
+  </si>
+  <si>
+    <t>cell.Value</t>
+  </si>
+  <si>
+    <t>Are Equal?</t>
+  </si>
+  <si>
+    <t>A2+$B$2</t>
+  </si>
+  <si>
+    <t>RC[-2]+R2C2</t>
+  </si>
+  <si>
+    <t>A3+$B$3</t>
+  </si>
+  <si>
+    <t>RC[-2]+R3C2</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>"Test" &amp; A4 &amp; "R3C2"</t>
+  </si>
+  <si>
+    <t>"Test" &amp; RC[-2] &amp; "R3C2"</t>
+  </si>
+  <si>
+    <t>TestAR3C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Array Formula: </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,169 +417,169 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:G14"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="7" width="10.282054" style="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:7">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:f>A2+$B$2</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F2" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="str">
-        <x:f>IF(C2=F2,"Yes", "No")</x:f>
-        <x:v>Yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:f>A3+$B$3</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="str">
-        <x:f>IF(C3=F3,"Yes", "No")</x:f>
-        <x:v>Yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="str">
-        <x:f>"Test" &amp; A4 &amp; "R3C2"</x:f>
-        <x:v>TestAR3C2</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="str">
-        <x:f>IF(C4=F4,"Yes", "No")</x:f>
-        <x:v>Yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:f t="array" ref="B6:B6">A2+A3</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:f t="array" ref="C6:D6">TRANSPOSE(A2:A3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0">
-        <x:f>A2 + A10_R1C1_A10_R1C1</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
-      <x:c r="A12" s="0">
-        <x:f>$A$2 + A10_R1C1_A10_R1C1</x:f>
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
-      <x:c r="A13" s="0">
-        <x:f>SUM(8:9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
-      <x:c r="A14" s="0">
-        <x:f>SUM(8:9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" style="0" customWidth="1" width="14.710625"/>
+    <col min="2" max="2" style="0" customWidth="1" width="6.139196"/>
+    <col min="3" max="3" style="0" customWidth="1" width="10.282054"/>
+    <col min="4" max="4" style="0" customWidth="1" width="19.853482"/>
+    <col min="5" max="5" style="0" customWidth="1" width="22.996339"/>
+    <col min="6" max="7" style="0" customWidth="1" width="10.282054"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0">
+        <v>2</v>
+      </c>
+      <c r="C2" s="0">
+        <f>A2+$B$2</f>
+        <v>3</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="0">
+        <v>3</v>
+      </c>
+      <c r="G2" s="0" t="str">
+        <f>IF(C2=F2,"Yes", "No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0">
+        <v>2</v>
+      </c>
+      <c r="C3" s="0">
+        <f>A3+$B$3</f>
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0">
+        <v>3</v>
+      </c>
+      <c r="G3" s="0" t="str">
+        <f>IF(C3=F3,"Yes", "No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f>"Test" &amp; A4 &amp; "R3C2"</f>
+        <v>TestAR3C2</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="0" t="str">
+        <f>IF(C4=F4,"Yes", "No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="0">
+        <f t="array" ref="B6:B6">A2+A3</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="0">
+        <f t="array" ref="C6:D6">TRANSPOSE(A2:A3)</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="0">
+        <f>A2 + A10_R1C1_A10_R1C1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="0">
+        <f>$A$2 + A10_R1C1_A10_R1C1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="0">
+        <f>SUM(8:9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="0">
+        <f>SUM(8:9)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>